--- a/output/pdf_financials_xlsx/BNS.xlsx
+++ b/output/pdf_financials_xlsx/BNS.xlsx
@@ -7539,22 +7539,22 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0</v>
+        <v>1.4e-05</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>0</v>
+        <v>7e-06</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>0</v>
+        <v>7e-06</v>
       </c>
       <c r="J122" s="1" t="inlineStr">
         <is>
@@ -50771,7 +50771,11 @@
           <t>Equity-settled share-based payment expense</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E563" t="inlineStr">
         <is>
           <t>-</t>
